--- a/tool/package-generator/clients/template/package_definition.xlsx
+++ b/tool/package-generator/clients/template/package_definition.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5CFB04-DBFC-4BB3-BCC3-5331D707DE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B05491E-F650-4DC4-85FA-AA4CA62DDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -64,16 +64,6 @@
       <t>サキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>.\a\新規 テキスト ドキュメント.txt</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>.\config\package_definition.xlsx</t>
-  </si>
-  <si>
-    <t>.\config\README.md</t>
   </si>
 </sst>
 </file>
@@ -422,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -448,22 +438,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -472,7 +446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75150BA2-5956-4186-B987-ACE3C5F8C674}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -500,21 +474,8 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2"/>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -523,6 +484,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -717,27 +698,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -754,23 +734,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/template/package_definition.xlsx
+++ b/tool/package-generator/clients/template/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B05491E-F650-4DC4-85FA-AA4CA62DDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B71A1E3-D2A1-4A0E-8F38-7E5DE73FC536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -95,7 +95,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +105,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -121,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -130,6 +136,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -412,13 +421,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.3984375" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" customWidth="1"/>
+    <col min="2" max="2" width="40.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75150BA2-5956-4186-B987-ACE3C5F8C674}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="40.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -434,41 +464,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75150BA2-5956-4186-B987-ACE3C5F8C674}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.3984375" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -484,6 +480,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
@@ -492,15 +497,6 @@
     <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -699,20 +695,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
     <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tool/package-generator/clients/template/package_definition.xlsx
+++ b/tool/package-generator/clients/template/package_definition.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B71A1E3-D2A1-4A0E-8F38-7E5DE73FC536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817809FA-373B-45D5-B085-DEACDAC7B6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
+    <sheet name="テンプレート" sheetId="4" r:id="rId1"/>
     <sheet name="コースA" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テンプレート!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -62,6 +65,13 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>拡張子</t>
+    <rPh sb="0" eb="3">
+      <t>カクチョウシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -115,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -123,11 +133,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,10 +160,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -420,25 +448,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C557493E-E206-413D-AAEF-ECEBF522D742}">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.69921875" customWidth="1"/>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="60.69921875" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -447,24 +481,26 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="40.69921875" customWidth="1"/>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="60.69921875" customWidth="1"/>
+    <col min="3" max="4" width="30.69921875" customWidth="1"/>
+    <col min="5" max="5" width="60.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/tool/package-generator/clients/template/package_definition.xlsx
+++ b/tool/package-generator/clients/template/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817809FA-373B-45D5-B085-DEACDAC7B6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F89A5A-D4D8-47DB-9A9C-68D318034133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -74,6 +74,27 @@
       <t>カクチョウシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>.\サンプル</t>
+  </si>
+  <si>
+    <t>.\サンプル\サンプルファイルA.txt</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>.\サンプル\サンプルフォルダA</t>
+  </si>
+  <si>
+    <t>.\サンプル\サンプルフォルダA\サンプルファイルB.txt</t>
+  </si>
+  <si>
+    <t>.\サンプル\サンプルフォルダA\フォルダB</t>
+  </si>
+  <si>
+    <t>.\サンプル\サンプルフォルダA\フォルダB\サンプルファイルC.txt</t>
   </si>
 </sst>
 </file>
@@ -449,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C557493E-E206-413D-AAEF-ECEBF522D742}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -466,6 +487,63 @@
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
